--- a/data/samples/samples/PL-6-2-A12H_D06_2026-03-06.xlsx
+++ b/data/samples/samples/PL-6-2-A12H_D06_2026-03-06.xlsx
@@ -1046,28 +1046,28 @@
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>06:00 06:30 钻进至 2685.38 m，钻压 86 kN，转速 137 rpm，排量 28 L/s，钻时 14.9 m/h。</t>
+          <t>06:30 06:30 钻进至 2685.38 m，钻压 86 kN，转速 137 rpm，排量 28 L/s，钻时 14.9 m/h。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>08:00 08:30 接单根，耗时 12 分钟。</t>
+          <t>08:30 08:30 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>11:00 11:15 循环调整泥浆性能，密度提至 1.29 g/cm3，漏斗粘度 47 s。</t>
+          <t>11:15 11:15 循环调整泥浆性能，密度提至 1.29 g/cm3，漏斗粘度 47 s。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>13:00 13:30 接单根，耗时 12 分钟。</t>
+          <t>13:30 13:30 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
@@ -1081,14 +1081,14 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>19:00 19:45 接单根，耗时 12 分钟。</t>
+          <t>19:45 19:45 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>21:00 21:15 接单根，耗时 12 分钟。</t>
+          <t>21:15 21:15 接单根，耗时 12 分钟。</t>
         </is>
       </c>
     </row>
